--- a/artfynd/A 23226-2026 artfynd.xlsx
+++ b/artfynd/A 23226-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134149100</v>
       </c>
       <c r="B2" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>134148989</v>
       </c>
       <c r="B3" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>134148952</v>
       </c>
       <c r="B4" t="n">
-        <v>111243</v>
+        <v>111250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>134148907</v>
       </c>
       <c r="B5" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23226-2026 artfynd.xlsx
+++ b/artfynd/A 23226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134149100</v>
+        <v>134148989</v>
       </c>
       <c r="B2" t="n">
-        <v>101396</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -791,41 +790,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134148989</v>
+        <v>134149919</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>58131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103023</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577399</v>
+        <v>577324</v>
       </c>
       <c r="R3" t="n">
-        <v>6339916</v>
+        <v>6339987</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,7 +891,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,7 +912,7 @@
         <v>134148952</v>
       </c>
       <c r="B4" t="n">
-        <v>111250</v>
+        <v>111257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1024,7 @@
         <v>134148907</v>
       </c>
       <c r="B5" t="n">
-        <v>106317</v>
+        <v>106324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,6 +1138,242 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134149319</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102637</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väster Hjortshult, Norra Fagerhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577386</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6339968</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anneli Brenander, Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134149100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Väster Hjortshult, Norra Fagerhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577399</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6339916</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23226-2026 artfynd.xlsx
+++ b/artfynd/A 23226-2026 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 23226-2026 artfynd.xlsx
+++ b/artfynd/A 23226-2026 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 23226-2026 artfynd.xlsx
+++ b/artfynd/A 23226-2026 artfynd.xlsx
@@ -1134,7 +1134,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 23226-2026 artfynd.xlsx
+++ b/artfynd/A 23226-2026 artfynd.xlsx
@@ -1134,7 +1134,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
